--- a/building_inspector_forms/015_core_building_assessment_form--building_inspector_forms.xlsx
+++ b/building_inspector_forms/015_core_building_assessment_form--building_inspector_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>safety_features</t>
+          <t>safety_features_2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Safety Features</t>
+          <t>Safety Features 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>exit_signs</t>
+          <t>exit_signs_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Exit Signs</t>
+          <t>Exit Signs 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>sprinkler_systems</t>
+          <t>sprinkler_systems_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sprinkler Systems</t>
+          <t>Sprinkler Systems 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -1185,7 +1185,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>safety_features_choices</t>
+          <t>safety_features_2_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1202,7 +1202,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>safety_features_choices</t>
+          <t>safety_features_2_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1219,7 +1219,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>safety_features_choices</t>
+          <t>safety_features_2_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1236,7 +1236,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>safety_features_choices</t>
+          <t>safety_features_2_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1423,7 +1423,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>exit_signs_choices</t>
+          <t>exit_signs_2_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1440,7 +1440,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>exit_signs_choices</t>
+          <t>exit_signs_2_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1457,7 +1457,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>sprinkler_systems_choices</t>
+          <t>sprinkler_systems_2_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1474,7 +1474,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>sprinkler_systems_choices</t>
+          <t>sprinkler_systems_2_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
